--- a/data/Links_test.xlsx
+++ b/data/Links_test.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="6">
   <si>
     <t>IFSCA</t>
   </si>
@@ -26,14 +26,14 @@
     <t>RBI</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t xml:space="preserve">Companies Act
 </t>
   </si>
   <si>
     <t>Listed Companies</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>SEBI</t>
@@ -44,7 +44,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -68,12 +68,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -140,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -157,12 +151,6 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -170,6 +158,12 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
@@ -185,9 +179,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -518,8 +509,8 @@
       <c r="B4" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="16"/>
-      <c r="B5" s="16"/>
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="15"/>
@@ -547,7 +538,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="5" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="10" width="61.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="61.43357142857143" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="5" width="13.005" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="5" width="13.005" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="5" width="13.005" customWidth="1" bestFit="1"/>
@@ -572,7 +563,7 @@
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -595,11 +586,11 @@
       <c r="U1" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="6" t="s">
-        <v>2</v>
+      <c r="A2" s="9" t="s">
+        <v>4</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>2</v>
+      <c r="B2" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -622,11 +613,11 @@
       <c r="U2" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="6" t="s">
-        <v>2</v>
+      <c r="A3" s="9" t="s">
+        <v>4</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>2</v>
+      <c r="B3" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -23646,7 +23637,7 @@
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -23815,7 +23806,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="1"/>
-      <c r="B7" s="9"/>
+      <c r="B7" s="7"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -51659,7 +51650,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="5" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="10" width="40.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="40.57642857142857" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -51668,53 +51659,37 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="31.5">
-      <c r="A2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="31.5">
-      <c r="A3" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="31.5">
-      <c r="A4" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="31.5">
-      <c r="A5" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>2</v>
-      </c>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1"/>
+      <c r="B2" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1"/>
+      <c r="B3" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1"/>
+      <c r="B4" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="1"/>
+      <c r="B5" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="8"/>
+      <c r="A6" s="6"/>
       <c r="B6" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="8"/>
+      <c r="A7" s="6"/>
       <c r="B7" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="8"/>
+      <c r="A8" s="6"/>
       <c r="B8" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="1"/>
-      <c r="B9" s="9"/>
+      <c r="B9" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
